--- a/data/naver_webtoon_series_mapping_duplicate_rows.xlsx
+++ b/data/naver_webtoon_series_mapping_duplicate_rows.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:08</t>
+          <t>2026-08-24 10:21:50</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:09</t>
+          <t>2026-08-24 10:21:50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:09</t>
+          <t>2026-08-24 10:21:51</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:09</t>
+          <t>2026-08-24 10:21:51</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:10</t>
+          <t>2026-08-24 10:21:51</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:10</t>
+          <t>2026-08-24 10:21:52</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:11</t>
+          <t>2026-08-24 10:21:53</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:12</t>
+          <t>2026-08-24 10:21:53</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:13</t>
+          <t>2026-08-24 10:21:53</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -2103,99 +2103,269 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>그랬더니 남친임니다</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853326&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>853326</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:21:53</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>뽀꼬</t>
+        </is>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>화, 금 연재</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>그랬더니 남친임니다</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>그랬더니 남친임니다 (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 뽀꼬 뽀꼬 | 2026.08.13. | 총6화/미완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 뽀꼬 뽀꼬 | 2026.08.13. | 총6화/미완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14536751</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>14536751</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>그랬더니 남친임니다 (총 6화/미완결)
+평점
+10.0 | 뽀꼬 뽀꼬 | 2026.08.13. | 총6화/미완결 | 3화 무료
+회사에 내 이상형이 입사했다?! 마주친 날부터 제대로 고장 난 그녀,어리둥절 실수로 데이트 신청까지 던져버리고 마는데…!어어, 근데 이때부터 이상하게 흘러간다?눈이 마주친 순간부터 연애까지,100% 리얼 실화로 달리는..</t>
+        </is>
+      </c>
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>145</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>1.7만</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>17000</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>41</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>생활의 참견 2 : 지금은 가족시절</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=849676&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>849676</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:13</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:21:54</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>김양수</t>
         </is>
       </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>화, 금 연재</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>생활의 참견 2 : 지금은 가족시절</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>생활의 참견 2 : 지금은 가족시절 (총 20화/미완결)</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>총 20화/미완결</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>20</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>평점 10.0 | 김양수 | 2026.06.08. | 총20화/미완결 | 15화 무료</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14011888</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>14011888</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>생활의 참견 2 : 지금은 가족시절 (총 20화/미완결)
 평점
@@ -2203,176 +2373,6 @@
 쉽게 지나치는 일상과 지나간 추억 속에서 발견하는 유쾌한 웃음,자라난 아이들과 더욱 강력해진 케미로 그가 돌아왔다!</t>
         </is>
       </c>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>145</v>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>2.4만</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>24000</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>화</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>53</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>그랬더니 남친임니다</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853326&amp;tab=tue</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>853326</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:13</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>뽀꼬</t>
-        </is>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>화, 금 연재</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>그랬더니 남친임니다</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>그랬더니 남친임니다 (총 6화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>총 6화/미완결</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>6</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 뽀꼬 뽀꼬 | 2026.08.13. | 총6화/미완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 뽀꼬 뽀꼬 | 2026.08.13. | 총6화/미완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14536751</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>14536751</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>그랬더니 남친임니다 (총 6화/미완결)
-평점
-10.0 | 뽀꼬 뽀꼬 | 2026.08.13. | 총6화/미완결 | 3화 무료
-회사에 내 이상형이 입사했다?! 마주친 날부터 제대로 고장 난 그녀,어리둥절 실수로 데이트 신청까지 던져버리고 마는데…!어어, 근데 이때부터 이상하게 흘러간다?눈이 마주친 순간부터 연애까지,100% 리얼 실화로 달리는..</t>
-        </is>
-      </c>
       <c r="Y12" t="b">
         <v>0</v>
       </c>
@@ -2402,11 +2402,11 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>1.7만</t>
+          <t>2.4만</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>17000</v>
+        <v>24000</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>searched_series</t>
+          <t>reused_existing_product_no</t>
         </is>
       </c>
       <c r="AJ12" t="b">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:14</t>
+          <t>2026-08-24 10:21:54</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:14</t>
+          <t>2026-08-24 10:21:54</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:14</t>
+          <t>2026-08-24 10:21:54</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:14</t>
+          <t>2026-08-24 10:21:54</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:14</t>
+          <t>2026-08-24 10:21:55</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -3273,27 +3273,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>중대장은 실망했다</t>
+          <t>어린이집 다니는 구나</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=841639&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=817945&amp;tab=wed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>841639</t>
+          <t>817945</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:16</t>
+          <t>2026-08-24 10:21:57</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>이량</t>
+          <t>구나</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -3306,17 +3306,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>월, 수 연재</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon,wed</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon,wed</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3324,21 +3324,21 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>중대장은 실망했다</t>
+          <t>어린이집 다니는 구나</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>중대장은 실망했다 (총 90화/미완결)</t>
+          <t>어린이집 다니는 구나 (총 187화/미완결)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>총 90화/미완결</t>
+          <t>총 187화/미완결</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3347,21 +3347,187 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>평점 9.9 | 이량 이량 | 2026.06.05. | 총90화/미완결 | 80화 무료</t>
+          <t>평점 10.0 | 구나 구나 | 2026.06.07. | 총187화/미완결 | 181화 무료</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=10301137</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>10301137</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>어린이집 다니는 구나 (총 187화/미완결)
+평점
+10.0 | 구나 구나 | 2026.06.07. | 총187화/미완결 | 181화 무료
+"노는 게 제일 좋아!" 라고 했더니 정말 노는 게 직업이 됐다?! 매일 동심의 세계로 출퇴근한지 어쩌다 10년째!아이들이라면 알 만큼 안다고 생각했는데... 예측불가한 말과 행동들은 여전히 새롭기만 하다. 그런 아이들에게 언제..</t>
+        </is>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>145</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>174.9만</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1749000</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>29</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>중대장은 실망했다</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841639&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>841639</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:21:57</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>이량</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>수, 토 연재</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>중대장은 실망했다</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>중대장은 실망했다 (총 90화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>총 90화/미완결</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>90</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>평점 9.9 | 이량 이량 | 2026.06.05. | 총90화/미완결 | 80화 무료</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13001011</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>13001011</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>중대장은 실망했다 (총 90화/미완결)
 평점
@@ -3369,172 +3535,6 @@
 마흔 살이 넘은 중대장은 멋진 모습을 보이고 싶지만요즘 애들, 요즘 군대는 왜 이렇게 변해버린 것일까!참으로.. 중대장은 실망했다!</t>
         </is>
       </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>145</v>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>103.8만</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1038000</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>31</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>어린이집 다니는 구나</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=817945&amp;tab=wed</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>817945</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:16</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>구나</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>월, 수 연재</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>mon,wed</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>mon,wed</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>어린이집 다니는 구나</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>어린이집 다니는 구나 (총 187화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>총 187화/미완결</t>
-        </is>
-      </c>
-      <c r="R19" t="n">
-        <v>187</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 구나 구나 | 2026.06.07. | 총187화/미완결 | 181화 무료</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=10301137</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>10301137</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>어린이집 다니는 구나 (총 187화/미완결)
-평점
-10.0 | 구나 구나 | 2026.06.07. | 총187화/미완결 | 181화 무료
-"노는 게 제일 좋아!" 라고 했더니 정말 노는 게 직업이 됐다?! 매일 동심의 세계로 출퇴근한지 어쩌다 10년째!아이들이라면 알 만큼 안다고 생각했는데... 예측불가한 말과 행동들은 여전히 새롭기만 하다. 그런 아이들에게 언제..</t>
-        </is>
-      </c>
       <c r="Y19" t="b">
         <v>0</v>
       </c>
@@ -3564,11 +3564,11 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>174.9만</t>
+          <t>103.8만</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1749000</v>
+        <v>1038000</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:17</t>
+          <t>2026-08-24 10:21:57</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:17</t>
+          <t>2026-08-24 10:21:58</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:18</t>
+          <t>2026-08-24 10:21:58</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:18</t>
+          <t>2026-08-24 10:21:58</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:18</t>
+          <t>2026-08-24 10:21:58</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:18</t>
+          <t>2026-08-24 10:21:59</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:19</t>
+          <t>2026-08-24 10:21:59</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:19</t>
+          <t>2026-08-24 10:21:59</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:19</t>
+          <t>2026-08-24 10:21:59</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:19</t>
+          <t>2026-08-24 10:22:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:20</t>
+          <t>2026-08-24 10:22:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:20</t>
+          <t>2026-08-24 10:22:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:20</t>
+          <t>2026-08-24 10:22:01</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:22</t>
+          <t>2026-08-24 10:22:02</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:22</t>
+          <t>2026-08-24 10:22:02</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:22</t>
+          <t>2026-08-24 10:22:03</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:23</t>
+          <t>2026-08-24 10:22:03</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -6354,99 +6354,269 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>그랬더니 남친임니다</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853326&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>853326</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:22:03</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>뽀꼬</t>
+        </is>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>화, 금 연재</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>그랬더니 남친임니다</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>그랬더니 남친임니다 (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>6</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 뽀꼬 뽀꼬 | 2026.08.13. | 총6화/미완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 뽀꼬 뽀꼬 | 2026.08.13. | 총6화/미완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14536751</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>14536751</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>그랬더니 남친임니다 (총 6화/미완결)
+평점
+10.0 | 뽀꼬 뽀꼬 | 2026.08.13. | 총6화/미완결 | 3화 무료
+회사에 내 이상형이 입사했다?! 마주친 날부터 제대로 고장 난 그녀,어리둥절 실수로 데이트 신청까지 던져버리고 마는데…!어어, 근데 이때부터 이상하게 흘러간다?눈이 마주친 순간부터 연애까지,100% 리얼 실화로 달리는..</t>
+        </is>
+      </c>
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>145</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>1.7만</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>17000</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>39</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>생활의 참견 2 : 지금은 가족시절</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=849676&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>849676</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:23</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:22:03</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>김양수</t>
         </is>
       </c>
-      <c r="I37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>화, 금 연재</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>생활의 참견 2 : 지금은 가족시절</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>생활의 참견 2 : 지금은 가족시절 (총 20화/미완결)</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>총 20화/미완결</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="R38" t="n">
         <v>20</v>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>평점 10.0 | 김양수 | 2026.06.08. | 총20화/미완결 | 15화 무료</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14011888</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>14011888</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>생활의 참견 2 : 지금은 가족시절 (총 20화/미완결)
 평점
@@ -6454,165 +6624,165 @@
 쉽게 지나치는 일상과 지나간 추억 속에서 발견하는 유쾌한 웃음,자라난 아이들과 더욱 강력해진 케미로 그가 돌아왔다!</t>
         </is>
       </c>
-      <c r="Y37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA37" t="n">
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
         <v>145</v>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD37" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF37" t="inlineStr">
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr">
         <is>
           <t>2.4만</t>
         </is>
       </c>
-      <c r="AG37" t="n">
+      <c r="AG38" t="n">
         <v>24000</v>
       </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C39" t="n">
         <v>47</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>구야는 신입</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=828167&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>828167</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:23</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:22:03</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>구야</t>
         </is>
       </c>
-      <c r="I38" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>월, 금 연재</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>mon,fri</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>mon,fri</t>
         </is>
       </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>구야는 신입</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>구야는 신입 (총 182화/미완결)</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>총 182화/미완결</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="R39" t="n">
         <v>182</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>평점 9.9 | 구야 구야 | 2026.06.07. | 총182화/미완결 | 178화 무료</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11367370</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>11367370</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>구야는 신입 (총 182화/미완결)
 평점
@@ -6620,176 +6790,6 @@
 평생 학생일 줄 알았던 내가 어느새 직장인이 되어버렸다.직장인이 된 기쁨도 잠시... 이제는 일하다가 몰래 잡코리x만 뒤져보는 직장인이 되어버렸다는데...사회초년생 구야의 웃픈(?) 홀로서기</t>
         </is>
       </c>
-      <c r="Y38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>145</v>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>50.9만</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>509000</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>48</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>그랬더니 남친임니다</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853326&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>853326</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:23</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>뽀꼬</t>
-        </is>
-      </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>화, 금 연재</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>그랬더니 남친임니다</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>그랬더니 남친임니다 (총 6화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>총 6화/미완결</t>
-        </is>
-      </c>
-      <c r="R39" t="n">
-        <v>6</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 뽀꼬 뽀꼬 | 2026.08.13. | 총6화/미완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 뽀꼬 뽀꼬 | 2026.08.13. | 총6화/미완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14536751</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>14536751</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>그랬더니 남친임니다 (총 6화/미완결)
-평점
-10.0 | 뽀꼬 뽀꼬 | 2026.08.13. | 총6화/미완결 | 3화 무료
-회사에 내 이상형이 입사했다?! 마주친 날부터 제대로 고장 난 그녀,어리둥절 실수로 데이트 신청까지 던져버리고 마는데…!어어, 근데 이때부터 이상하게 흘러간다?눈이 마주친 순간부터 연애까지,100% 리얼 실화로 달리는..</t>
-        </is>
-      </c>
       <c r="Y39" t="b">
         <v>0</v>
       </c>
@@ -6819,11 +6819,11 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>1.7만</t>
+          <t>50.9만</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>17000</v>
+        <v>509000</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>searched_series</t>
+          <t>reused_existing_product_no</t>
         </is>
       </c>
       <c r="AJ39" t="b">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:23</t>
+          <t>2026-08-24 10:22:04</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:23</t>
+          <t>2026-08-24 10:22:04</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:24</t>
+          <t>2026-08-24 10:22:04</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:26</t>
+          <t>2026-08-24 10:22:06</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:26</t>
+          <t>2026-08-24 10:22:06</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:26</t>
+          <t>2026-08-24 10:22:06</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:26</t>
+          <t>2026-08-24 10:22:06</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:27</t>
+          <t>2026-08-24 10:22:07</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:27</t>
+          <t>2026-08-24 10:22:07</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -8354,7 +8354,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:27</t>
+          <t>2026-08-24 10:22:07</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:27</t>
+          <t>2026-08-24 10:22:07</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:28</t>
+          <t>2026-08-24 10:22:07</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:28</t>
+          <t>2026-08-24 10:22:07</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:30</t>
+          <t>2026-08-24 10:22:08</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:30</t>
+          <t>2026-08-24 10:22:09</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:30</t>
+          <t>2026-08-24 10:22:09</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:31</t>
+          <t>2026-08-24 10:22:09</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:31</t>
+          <t>2026-08-24 10:22:09</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:33</t>
+          <t>2026-08-24 10:22:11</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
